--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484199_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484199_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.3713</v>
+        <v>0.4497</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9564</v>
+        <v>3.8442</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.5851</v>
+        <v>-3.3944</v>
       </c>
       <c r="G2" t="n">
         <v>-0.2568</v>
@@ -610,13 +610,13 @@
         <v>1.9534</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2608</v>
+        <v>0.3391</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3003</v>
+        <v>1.188</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0395</v>
+        <v>-0.8489</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6093</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.5812</v>
+        <v>-0.2953</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4896</v>
+        <v>0.1776</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0916</v>
+        <v>-0.4729</v>
       </c>
       <c r="G3" t="n">
         <v>-1.5024</v>
@@ -688,13 +688,13 @@
         <v>1.5627</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.356</v>
+        <v>-0.0701</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3135</v>
+        <v>0.3537</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0426</v>
+        <v>-0.4239</v>
       </c>
       <c r="V3" t="n">
         <v>0.8865</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.1192</v>
+        <v>-1.3409</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8925</v>
+        <v>-1.1958</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2267</v>
+        <v>-0.145</v>
       </c>
       <c r="G4" t="n">
         <v>-0.4792</v>
@@ -766,13 +766,13 @@
         <v>0.9767</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1563</v>
+        <v>-0.0653</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4458</v>
+        <v>0.1424</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2895</v>
+        <v>-0.2078</v>
       </c>
       <c r="V4" t="n">
         <v>-1.7731</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.259</v>
+        <v>-3.0895</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8988</v>
+        <v>-0.8381999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.3602</v>
+        <v>-2.2513</v>
       </c>
       <c r="G5" t="n">
         <v>-1.6364</v>
@@ -844,13 +844,13 @@
         <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2955</v>
+        <v>0.465</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5063</v>
+        <v>0.5668</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2108</v>
+        <v>-0.1018</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9414</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-4.4803</v>
+        <v>-3.9742</v>
       </c>
       <c r="E6" t="n">
-        <v>-5.1083</v>
+        <v>-4.6839</v>
       </c>
       <c r="F6" t="n">
-        <v>0.628</v>
+        <v>0.7097</v>
       </c>
       <c r="G6" t="n">
         <v>-1.5403</v>
@@ -922,13 +922,13 @@
         <v>2.1488</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2992</v>
+        <v>-0.7931</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0246</v>
+        <v>0.3998</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.2745</v>
+        <v>-1.1928</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6642</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. DIALLO BADJI</t>
+          <t>A. REBOLLO BONET</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-7.2478</v>
+        <v>-6.7679</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.6237</v>
+        <v>-2.9213</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.6241</v>
+        <v>-3.8467</v>
       </c>
       <c r="G7" t="n">
-        <v>-7.3043</v>
+        <v>-4.6733</v>
       </c>
       <c r="H7" t="n">
-        <v>-5.5506</v>
+        <v>-1.6119</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.7536</v>
+        <v>-3.0614</v>
       </c>
       <c r="J7" t="n">
-        <v>-4.633</v>
+        <v>-0.2998</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.2848</v>
+        <v>2.3561</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3482</v>
+        <v>-2.6559</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.6712</v>
+        <v>-4.3735</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.2658</v>
+        <v>-3.968</v>
       </c>
       <c r="O7" t="n">
         <v>-0.4054</v>
       </c>
       <c r="P7" t="n">
-        <v>0.586</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1488</v>
+        <v>-4.8836</v>
       </c>
       <c r="R7" t="n">
         <v>2.7348</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8528</v>
+        <v>-0.61</v>
       </c>
       <c r="T7" t="n">
-        <v>2.4902</v>
+        <v>0.4342</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6374</v>
+        <v>-1.0442</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.3824</v>
+        <v>0.6642</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3321</v>
+        <v>1.8279</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.0503</v>
+        <v>-1.1638</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. REBOLLO BONET</t>
+          <t>M. PERONA MARCH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-7.4642</v>
+        <v>-7.4853</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.4268</v>
+        <v>-6.2796</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.0373</v>
+        <v>-1.2057</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.6733</v>
+        <v>-1.7101</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6119</v>
+        <v>0.0696</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.0614</v>
+        <v>-1.7797</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2998</v>
+        <v>-0.6573</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3561</v>
+        <v>1.3917</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.6559</v>
+        <v>-2.0489</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.3735</v>
+        <v>-1.0528</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.968</v>
+        <v>-1.3221</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4054</v>
+        <v>0.2692</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.1488</v>
+        <v>-5.2743</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.8836</v>
+        <v>-7.0323</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7348</v>
+        <v>1.7581</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3062</v>
+        <v>-1.1652</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.07140000000000001</v>
+        <v>0.1914</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2349</v>
+        <v>-1.3565</v>
       </c>
       <c r="V8" t="n">
         <v>0.6642</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8279</v>
+        <v>1.2186</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1638</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. BENNASSAR ROSSELLÓ</t>
+          <t>M. VAN ZUUREN ABAD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-8.556100000000001</v>
+        <v>-8.1114</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.0105</v>
+        <v>-3.2232</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5456</v>
+        <v>-4.8882</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.676</v>
+        <v>-4.6599</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5201</v>
+        <v>-2.273</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.1559</v>
+        <v>-2.3869</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3208</v>
+        <v>-2.1238</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2947</v>
+        <v>-0.142</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.6155</v>
+        <v>-1.9818</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.3552</v>
+        <v>-2.536</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.8148</v>
+        <v>-2.131</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5405</v>
+        <v>-0.4051</v>
       </c>
       <c r="P9" t="n">
-        <v>-5.4696</v>
+        <v>0.1953</v>
       </c>
       <c r="Q9" t="n">
-        <v>-8.009</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5395</v>
+        <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0198</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>0.71</v>
+        <v>0.5415</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7298</v>
+        <v>-0.5325</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6093</v>
+        <v>-3.6559</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6093</v>
+        <v>-0.6642</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.9917</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. VAN ZUUREN ABAD</t>
+          <t>A. BENNASSAR ROSSELLÓ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.6503</v>
+        <v>-8.686199999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7893</v>
+        <v>-6.95</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.861</v>
+        <v>-1.7363</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.6599</v>
+        <v>-3.676</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.273</v>
+        <v>-0.5201</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.3869</v>
+        <v>-3.1559</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.1238</v>
+        <v>-0.3208</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.142</v>
+        <v>2.2947</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.9818</v>
+        <v>-2.6155</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.536</v>
+        <v>-3.3552</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.131</v>
+        <v>-2.8148</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4051</v>
+        <v>-0.5405</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1953</v>
+        <v>-5.4696</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-8.009</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1721</v>
+        <v>2.5395</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5299</v>
+        <v>-0.15</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0246</v>
+        <v>0.7705</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5053</v>
+        <v>-0.9205</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.6559</v>
+        <v>0.6093</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6642</v>
+        <v>0.6093</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.9917</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. PERONA MARCH</t>
+          <t>M. DIALLO BADJI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.7265</v>
+        <v>-8.806900000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.4118</v>
+        <v>-6.0194</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3147</v>
+        <v>-2.7876</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7101</v>
+        <v>-7.3043</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0696</v>
+        <v>-5.5506</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.7797</v>
+        <v>-1.7536</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6573</v>
+        <v>-4.633</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3917</v>
+        <v>-3.2848</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.0489</v>
+        <v>-1.3482</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0528</v>
+        <v>-2.6712</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3221</v>
+        <v>-2.2658</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2692</v>
+        <v>-0.4054</v>
       </c>
       <c r="P11" t="n">
-        <v>-5.2743</v>
+        <v>0.586</v>
       </c>
       <c r="Q11" t="n">
-        <v>-7.0323</v>
+        <v>-2.1488</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7581</v>
+        <v>2.7348</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.4063</v>
+        <v>0.2937</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9408</v>
+        <v>1.0945</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.4655</v>
+        <v>-0.8008</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6642</v>
+        <v>-2.3824</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2186</v>
+        <v>-0.3321</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5545</v>
+        <v>-2.0503</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-48.7133</v>
+        <v>-48.1079</v>
       </c>
       <c r="E12" t="n">
-        <v>-28.6949</v>
+        <v>-28.0896</v>
       </c>
       <c r="F12" t="n">
-        <v>-20.0183</v>
+        <v>-20.0184</v>
       </c>
       <c r="G12" t="n">
         <v>-27.4387</v>
@@ -1363,10 +1363,10 @@
         <v>-11.4636</v>
       </c>
       <c r="J12" t="n">
-        <v>-6.821099999999999</v>
+        <v>-6.8211</v>
       </c>
       <c r="K12" t="n">
-        <v>3.9624</v>
+        <v>3.962399999999999</v>
       </c>
       <c r="L12" t="n">
         <v>-10.7835</v>
@@ -1390,13 +1390,13 @@
         <v>18.5576</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.352</v>
+        <v>-1.7469</v>
       </c>
       <c r="T12" t="n">
-        <v>5.0777</v>
+        <v>5.6828</v>
       </c>
       <c r="U12" t="n">
-        <v>-7.4298</v>
+        <v>-7.4297</v>
       </c>
       <c r="V12" t="n">
         <v>-7.2021</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.5975</v>
+        <v>7.5815</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8875</v>
+        <v>2.3931</v>
       </c>
       <c r="F13" t="n">
-        <v>5.71</v>
+        <v>5.1885</v>
       </c>
       <c r="G13" t="n">
         <v>3.9677</v>
@@ -1468,13 +1468,13 @@
         <v>3.3208</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2038</v>
+        <v>1.1878</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1432</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0606</v>
+        <v>0.5391</v>
       </c>
       <c r="V13" t="n">
         <v>0.2772</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.7288</v>
+        <v>7.1558</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4693</v>
+        <v>3.8895</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2595</v>
+        <v>3.2662</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9518</v>
+        <v>3.0311</v>
       </c>
       <c r="H14" t="n">
-        <v>0.968</v>
+        <v>1.8033</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9838</v>
+        <v>1.2278</v>
       </c>
       <c r="J14" t="n">
-        <v>1.088</v>
+        <v>1.9671</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0476</v>
+        <v>2.0875</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0405</v>
+        <v>-0.1204</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8638</v>
+        <v>1.064</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0795</v>
+        <v>-0.2842</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9433</v>
+        <v>1.3482</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9534</v>
+        <v>2.3441</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1488</v>
+        <v>2.5395</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3863</v>
+        <v>0.5619</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8035</v>
+        <v>0.3447</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4172</v>
+        <v>0.2173</v>
       </c>
       <c r="V14" t="n">
-        <v>2.4373</v>
+        <v>1.2186</v>
       </c>
       <c r="W14" t="n">
         <v>1.7731</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6642</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.2587</v>
+        <v>7.1425</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1817</v>
+        <v>3.3682</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0769</v>
+        <v>3.7743</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0311</v>
+        <v>1.9518</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8033</v>
+        <v>0.968</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2278</v>
+        <v>0.9838</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9671</v>
+        <v>1.088</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0875</v>
+        <v>1.0476</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1204</v>
+        <v>0.0405</v>
       </c>
       <c r="M15" t="n">
-        <v>1.064</v>
+        <v>0.8638</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2842</v>
+        <v>-0.0795</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3482</v>
+        <v>0.9433</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3441</v>
+        <v>1.9534</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5395</v>
+        <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3352</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3631</v>
+        <v>0.7024</v>
       </c>
       <c r="U15" t="n">
-        <v>0.028</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2186</v>
+        <v>2.4373</v>
       </c>
       <c r="W15" t="n">
         <v>1.7731</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5545</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.2215</v>
+        <v>6.9631</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4069</v>
+        <v>4.0136</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8146</v>
+        <v>2.9494</v>
       </c>
       <c r="G16" t="n">
         <v>2.9426</v>
@@ -1702,13 +1702,13 @@
         <v>2.9301</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9713000000000001</v>
+        <v>-0.2298</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2283</v>
+        <v>0.3784</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.743</v>
+        <v>-0.6082</v>
       </c>
       <c r="V16" t="n">
         <v>2.4921</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.6512</v>
+        <v>5.9065</v>
       </c>
       <c r="E17" t="n">
-        <v>4.1504</v>
+        <v>2.8627</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5008</v>
+        <v>3.0438</v>
       </c>
       <c r="G17" t="n">
-        <v>6.4344</v>
+        <v>2.4476</v>
       </c>
       <c r="H17" t="n">
-        <v>5.1536</v>
+        <v>1.8276</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2809</v>
+        <v>0.62</v>
       </c>
       <c r="J17" t="n">
-        <v>5.9941</v>
+        <v>1.3984</v>
       </c>
       <c r="K17" t="n">
-        <v>5.7918</v>
+        <v>1.9915</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2023</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4403</v>
+        <v>1.0492</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6382</v>
+        <v>-0.1639</v>
       </c>
       <c r="O17" t="n">
-        <v>1.0786</v>
+        <v>1.2132</v>
       </c>
       <c r="P17" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.1488</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.9863</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.1405</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.1542</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.4959</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.4959</v>
+      </c>
+      <c r="X17" t="n">
         <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>-3.1255</v>
-      </c>
-      <c r="R17" t="n">
-        <v>3.1255</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.4902</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.0594</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-0.5691000000000001</v>
-      </c>
-      <c r="V17" t="n">
-        <v>-1.2735</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.2224</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-1.4959</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>5.2453</v>
+        <v>5.2999</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6605</v>
+        <v>3.7459</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5848</v>
+        <v>1.5539</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4476</v>
+        <v>6.4344</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8276</v>
+        <v>5.1536</v>
       </c>
       <c r="I18" t="n">
-        <v>0.62</v>
+        <v>1.2809</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3984</v>
+        <v>5.9941</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9915</v>
+        <v>5.7918</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.2023</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0492</v>
+        <v>0.4403</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1639</v>
+        <v>-0.6382</v>
       </c>
       <c r="O18" t="n">
-        <v>1.2132</v>
+        <v>1.0786</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1721</v>
+        <v>-3.1255</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1488</v>
+        <v>3.1255</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3252</v>
+        <v>0.1389</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9383</v>
+        <v>0.6549</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6132</v>
+        <v>-0.516</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4959</v>
+        <v>-1.2735</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4959</v>
+        <v>0.2224</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.3147</v>
+        <v>5.2949</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3107</v>
+        <v>3.0185</v>
       </c>
       <c r="F19" t="n">
-        <v>2.004</v>
+        <v>2.2764</v>
       </c>
       <c r="G19" t="n">
         <v>3.8132</v>
@@ -1936,13 +1936,13 @@
         <v>2.9301</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1115</v>
+        <v>-0.1314</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4099</v>
+        <v>0.2979</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7016</v>
+        <v>-0.4293</v>
       </c>
       <c r="V19" t="n">
         <v>0.8317</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.9846</v>
+        <v>2.384</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7006</v>
+        <v>-0.5995</v>
       </c>
       <c r="F20" t="n">
-        <v>2.6852</v>
+        <v>2.9834</v>
       </c>
       <c r="G20" t="n">
         <v>1.6262</v>
@@ -2014,13 +2014,13 @@
         <v>3.5162</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5514</v>
+        <v>-0.152</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3853</v>
+        <v>0.4864</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9366</v>
+        <v>-0.6384</v>
       </c>
       <c r="V20" t="n">
         <v>1.4959</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.8705</v>
+        <v>1.623</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3304</v>
+        <v>-1.0382</v>
       </c>
       <c r="F21" t="n">
-        <v>2.201</v>
+        <v>2.6612</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3375</v>
@@ -2092,13 +2092,13 @@
         <v>2.3441</v>
       </c>
       <c r="S21" t="n">
-        <v>1.7587</v>
+        <v>1.5112</v>
       </c>
       <c r="T21" t="n">
-        <v>2.2865</v>
+        <v>1.5787</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5278</v>
+        <v>-0.0675</v>
       </c>
       <c r="V21" t="n">
         <v>0.2772</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>M. TOLEDO CIVICO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.2618</v>
+        <v>1.2103</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0336</v>
+        <v>0.0183</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2953</v>
+        <v>1.192</v>
       </c>
       <c r="G22" t="n">
-        <v>1.8089</v>
+        <v>1.4841</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0253</v>
+        <v>0.8102</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8342</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7449</v>
+        <v>0.6152</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1241</v>
+        <v>0.6152</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6208</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.064</v>
+        <v>0.8688</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1494</v>
+        <v>0.1949</v>
       </c>
       <c r="O22" t="n">
-        <v>1.2134</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.1255</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7348</v>
+        <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3394</v>
+        <v>0.0034</v>
       </c>
       <c r="T22" t="n">
-        <v>2.347</v>
+        <v>0.1026</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0076</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.4959</v>
+        <v>-0.2772</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4959</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. TOLEDO CIVICO</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9614</v>
+        <v>0.4348</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1195</v>
+        <v>-1.3481</v>
       </c>
       <c r="F23" t="n">
-        <v>0.842</v>
+        <v>1.7829</v>
       </c>
       <c r="G23" t="n">
-        <v>1.4841</v>
+        <v>1.8089</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8102</v>
+        <v>-0.0253</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6739000000000001</v>
+        <v>1.8342</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6152</v>
+        <v>0.7449</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6152</v>
+        <v>0.1241</v>
       </c>
       <c r="L23" t="n">
+        <v>0.6208</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.064</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.1494</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.2134</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-3.1255</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.7348</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.0325</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.5201</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="W23" t="n">
         <v>0</v>
       </c>
-      <c r="M23" t="n">
-        <v>0.8688</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.1949</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0.6739000000000001</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>-0.9767</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.9767</v>
-      </c>
-      <c r="S23" t="n">
-        <v>-0.2454</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0.2037</v>
-      </c>
-      <c r="U23" t="n">
-        <v>-0.4491</v>
-      </c>
-      <c r="V23" t="n">
-        <v>-0.2772</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0.2772</v>
-      </c>
       <c r="X23" t="n">
-        <v>-0.5545</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6171</v>
+        <v>0.4135</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1035</v>
+        <v>-0.3057</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7206</v>
+        <v>0.7192</v>
       </c>
       <c r="G24" t="n">
         <v>-0.7317</v>
@@ -2326,13 +2326,13 @@
         <v>1.5627</v>
       </c>
       <c r="S24" t="n">
-        <v>0.06320000000000001</v>
+        <v>-0.1404</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2642</v>
+        <v>0.062</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.201</v>
+        <v>-0.2023</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2772</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>48.7131</v>
+        <v>51.4098</v>
       </c>
       <c r="E25" t="n">
-        <v>20.0184</v>
+        <v>20.0183</v>
       </c>
       <c r="F25" t="n">
-        <v>28.6947</v>
+        <v>31.3912</v>
       </c>
       <c r="G25" t="n">
         <v>27.43840000000001</v>
@@ -2404,13 +2404,13 @@
         <v>30.2781</v>
       </c>
       <c r="S25" t="n">
-        <v>2.352</v>
+        <v>5.048300000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>7.429799999999999</v>
+        <v>7.4297</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.077599999999999</v>
+        <v>-2.3811</v>
       </c>
       <c r="V25" t="n">
         <v>7.202100000000002</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484199_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484199_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,11 +549,16 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. BAUZA MEDINA</t>
+          <t>A. BENNASSAR ROSSELLÓ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +570,78 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4497</v>
+        <v>0.921</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8442</v>
+        <v>0.921</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.3944</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2568</v>
+        <v>0.921</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0.921</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2568</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>3.0236</v>
+        <v>0.921</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3356</v>
+        <v>0.921</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6879</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.2804</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.3356</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9447</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3391</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1.188</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8489</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. ZICOVICH</t>
+          <t>A. BAUZA MEDINA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +653,78 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2953</v>
+        <v>0.4497</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1776</v>
+        <v>3.8442</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4729</v>
+        <v>-3.3944</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.5024</v>
+        <v>-0.2568</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.0673</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5649</v>
+        <v>-0.2568</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1642</v>
+        <v>3.0236</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.9965000000000001</v>
+        <v>2.3356</v>
       </c>
       <c r="L3" t="n">
-        <v>1.1607</v>
+        <v>0.6879</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6666</v>
+        <v>-3.2804</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.0708</v>
+        <v>-2.3356</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4043</v>
+        <v>-0.9447</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5627</v>
+        <v>1.9534</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0701</v>
+        <v>0.3391</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3537</v>
+        <v>1.188</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4239</v>
+        <v>-0.8489</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8865</v>
+        <v>-0.6093</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8317</v>
+        <v>0.6093</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0549</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. BILBAO BORRAJO</t>
+          <t>B. ZICOVICH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.3409</v>
+        <v>-0.2953</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.1958</v>
+        <v>0.1776</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.145</v>
+        <v>-0.4729</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4792</v>
+        <v>-1.5024</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8836000000000001</v>
+        <v>-3.0673</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4045</v>
+        <v>1.5649</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6741</v>
+        <v>0.1642</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6741</v>
+        <v>-0.9965000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.1607</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1949</v>
+        <v>-1.6666</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2095</v>
+        <v>-2.0708</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4045</v>
+        <v>0.4043</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0653</v>
+        <v>-0.0701</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1424</v>
+        <v>0.3537</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2078</v>
+        <v>-0.4239</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.7731</v>
+        <v>0.8865</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6642</v>
+        <v>0.8317</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1089</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. VASCENCO BADRAJAN</t>
+          <t>A. BILBAO BORRAJO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.0895</v>
+        <v>-1.3409</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8381999999999999</v>
+        <v>-1.1958</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.2513</v>
+        <v>-0.145</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.6364</v>
+        <v>-0.4792</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5572</v>
+        <v>-0.8836000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0792</v>
+        <v>0.4045</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2711</v>
+        <v>-0.6741</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9452</v>
+        <v>-0.6741</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6741</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9075</v>
+        <v>0.1949</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5024</v>
+        <v>-0.2095</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4051</v>
+        <v>0.4045</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9767</v>
+        <v>0.9767</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>0.465</v>
+        <v>-0.0653</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5668</v>
+        <v>0.1424</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1018</v>
+        <v>-0.2078</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9414</v>
+        <v>-1.7731</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2772</v>
+        <v>-0.6642</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2186</v>
+        <v>-1.1089</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. HIDALGO GARRIGUES</t>
+          <t>N. VASCENCO BADRAJAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.9742</v>
+        <v>-3.0895</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.6839</v>
+        <v>-0.8381999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7097</v>
+        <v>-2.2513</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5403</v>
+        <v>-1.6364</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.5807</v>
+        <v>-0.5572</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0405</v>
+        <v>-1.0792</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.5712</v>
+        <v>0.2711</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2635</v>
+        <v>0.9452</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3077</v>
+        <v>-0.6741</v>
       </c>
       <c r="M6" t="n">
-        <v>0.031</v>
+        <v>-1.9075</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3172</v>
+        <v>-1.5024</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3482</v>
+        <v>-0.4051</v>
       </c>
       <c r="P6" t="n">
         <v>-0.9767</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.1255</v>
+        <v>-1.9534</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1488</v>
+        <v>0.9767</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7931</v>
+        <v>0.465</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3998</v>
+        <v>0.5668</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.1928</v>
+        <v>-0.1018</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6642</v>
+        <v>-0.9414</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3869</v>
+        <v>0.2772</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. REBOLLO BONET</t>
+          <t>B. HIDALGO GARRIGUES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-6.7679</v>
+        <v>-3.9742</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.9213</v>
+        <v>-4.6839</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.8467</v>
+        <v>0.7097</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.6733</v>
+        <v>-1.5403</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.6119</v>
+        <v>-1.5807</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.0614</v>
+        <v>0.0405</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2998</v>
+        <v>-1.5712</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3561</v>
+        <v>-0.2635</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.6559</v>
+        <v>-1.3077</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.3735</v>
+        <v>0.031</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.968</v>
+        <v>-1.3172</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4054</v>
+        <v>1.3482</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.8836</v>
+        <v>-3.1255</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7348</v>
+        <v>2.1488</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.61</v>
+        <v>-0.7931</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4342</v>
+        <v>0.3998</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0442</v>
+        <v>-1.1928</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6642</v>
+        <v>-0.6642</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8279</v>
+        <v>-0.3869</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1638</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. PERONA MARCH</t>
+          <t>A. REBOLLO BONET</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-7.4853</v>
+        <v>-6.7679</v>
       </c>
       <c r="E8" t="n">
-        <v>-6.2796</v>
+        <v>-2.9213</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2057</v>
+        <v>-3.8467</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7101</v>
+        <v>-4.6733</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0696</v>
+        <v>-1.6119</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.7797</v>
+        <v>-3.0614</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6573</v>
+        <v>-0.2998</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3917</v>
+        <v>2.3561</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.0489</v>
+        <v>-2.6559</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0528</v>
+        <v>-4.3735</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3221</v>
+        <v>-3.968</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2692</v>
+        <v>-0.4054</v>
       </c>
       <c r="P8" t="n">
-        <v>-5.2743</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q8" t="n">
-        <v>-7.0323</v>
+        <v>-4.8836</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7581</v>
+        <v>2.7348</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1652</v>
+        <v>-0.61</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1914</v>
+        <v>0.4342</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.3565</v>
+        <v>-1.0442</v>
       </c>
       <c r="V8" t="n">
         <v>0.6642</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2186</v>
+        <v>1.8279</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5545</v>
+        <v>-1.1638</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. VAN ZUUREN ABAD</t>
+          <t>M. PERONA MARCH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-8.1114</v>
+        <v>-7.4853</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2232</v>
+        <v>-6.2796</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.8882</v>
+        <v>-1.2057</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.6599</v>
+        <v>-1.7101</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.273</v>
+        <v>0.0696</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.3869</v>
+        <v>-1.7797</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.1238</v>
+        <v>-0.6573</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.142</v>
+        <v>1.3917</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.9818</v>
+        <v>-2.0489</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.536</v>
+        <v>-1.0528</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.131</v>
+        <v>-1.3221</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4051</v>
+        <v>0.2692</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1953</v>
+        <v>-5.2743</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-7.0323</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>0.008999999999999999</v>
+        <v>-1.1652</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5415</v>
+        <v>0.1914</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5325</v>
+        <v>-1.3565</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.6559</v>
+        <v>0.6642</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6642</v>
+        <v>1.2186</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.9917</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. BENNASSAR ROSSELLÓ</t>
+          <t>M. VAN ZUUREN ABAD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1234,72 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.686199999999999</v>
+        <v>-8.1114</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.95</v>
+        <v>-3.2232</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7363</v>
+        <v>-4.8882</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.676</v>
+        <v>-4.6599</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5201</v>
+        <v>-2.273</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.1559</v>
+        <v>-2.3869</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3208</v>
+        <v>-2.1238</v>
       </c>
       <c r="K10" t="n">
-        <v>2.2947</v>
+        <v>-0.142</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.6155</v>
+        <v>-1.9818</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.3552</v>
+        <v>-2.536</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.8148</v>
+        <v>-2.131</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5405</v>
+        <v>-0.4051</v>
       </c>
       <c r="P10" t="n">
-        <v>-5.4696</v>
+        <v>0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-8.009</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5395</v>
+        <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.15</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7705</v>
+        <v>0.5415</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9205</v>
+        <v>-0.5325</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6093</v>
+        <v>-3.6559</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6093</v>
+        <v>-0.6642</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.9917</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1329,11 +1379,16 @@
       <c r="X11" t="n">
         <v>-2.0503</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. BENNASSAR ROSSELLO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,457 +1400,483 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-48.1079</v>
+        <v>-9.607200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-28.0896</v>
+        <v>-7.8709</v>
       </c>
       <c r="F12" t="n">
-        <v>-20.0184</v>
+        <v>-1.7363</v>
       </c>
       <c r="G12" t="n">
-        <v>-27.4387</v>
+        <v>-4.597</v>
       </c>
       <c r="H12" t="n">
-        <v>-15.9748</v>
+        <v>-1.441</v>
       </c>
       <c r="I12" t="n">
-        <v>-11.4636</v>
+        <v>-3.1559</v>
       </c>
       <c r="J12" t="n">
-        <v>-6.8211</v>
+        <v>-1.2417</v>
       </c>
       <c r="K12" t="n">
-        <v>3.962399999999999</v>
+        <v>1.3737</v>
       </c>
       <c r="L12" t="n">
-        <v>-10.7835</v>
+        <v>-2.6155</v>
       </c>
       <c r="M12" t="n">
-        <v>-20.6173</v>
+        <v>-3.3552</v>
       </c>
       <c r="N12" t="n">
-        <v>-19.9372</v>
+        <v>-2.8148</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6799999999999998</v>
+        <v>-0.5405</v>
       </c>
       <c r="P12" t="n">
-        <v>-11.7207</v>
+        <v>-5.4696</v>
       </c>
       <c r="Q12" t="n">
-        <v>-30.2781</v>
+        <v>-8.009</v>
       </c>
       <c r="R12" t="n">
-        <v>18.5576</v>
+        <v>2.5395</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7469</v>
+        <v>-0.15</v>
       </c>
       <c r="T12" t="n">
-        <v>5.6828</v>
+        <v>0.7705</v>
       </c>
       <c r="U12" t="n">
-        <v>-7.4297</v>
+        <v>-0.9205</v>
       </c>
       <c r="V12" t="n">
-        <v>-7.2021</v>
+        <v>0.6093</v>
       </c>
       <c r="W12" t="n">
-        <v>3.3266</v>
+        <v>0.6093</v>
       </c>
       <c r="X12" t="n">
-        <v>-10.5287</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>CB ANDRATX</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.5815</v>
+        <v>-48.1079</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3931</v>
+        <v>-28.0895</v>
       </c>
       <c r="F13" t="n">
-        <v>5.1885</v>
+        <v>-20.0184</v>
       </c>
       <c r="G13" t="n">
-        <v>3.9677</v>
+        <v>-27.4387</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5388</v>
+        <v>-15.9747</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4289</v>
+        <v>-11.4636</v>
       </c>
       <c r="J13" t="n">
-        <v>2.6391</v>
+        <v>-6.821</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5582</v>
+        <v>3.962399999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0809</v>
+        <v>-10.7835</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3286</v>
+        <v>-20.6173</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0194</v>
+        <v>-19.9372</v>
       </c>
       <c r="O13" t="n">
-        <v>1.348</v>
+        <v>-0.6799999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1488</v>
+        <v>-11.7207</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1721</v>
+        <v>-30.27810000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>3.3208</v>
+        <v>18.5576</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1878</v>
+        <v>-1.7469</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6487000000000001</v>
+        <v>5.6828</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5391</v>
+        <v>-7.4297</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2772</v>
+        <v>-7.202099999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2772</v>
+        <v>3.326599999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
-      </c>
+        <v>-10.5287</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.1558</v>
+        <v>7.5815</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8895</v>
+        <v>2.3931</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2662</v>
+        <v>5.1885</v>
       </c>
       <c r="G14" t="n">
-        <v>3.0311</v>
+        <v>3.9677</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8033</v>
+        <v>2.5388</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2278</v>
+        <v>1.4289</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9671</v>
+        <v>2.6391</v>
       </c>
       <c r="K14" t="n">
-        <v>2.0875</v>
+        <v>2.5582</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1204</v>
+        <v>0.0809</v>
       </c>
       <c r="M14" t="n">
-        <v>1.064</v>
+        <v>1.3286</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2842</v>
+        <v>-0.0194</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3482</v>
+        <v>1.348</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3441</v>
+        <v>2.1488</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5395</v>
+        <v>3.3208</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5619</v>
+        <v>1.1878</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3447</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2173</v>
+        <v>0.5391</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7731</v>
+        <v>0.2772</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.1425</v>
+        <v>7.1558</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3682</v>
+        <v>3.8895</v>
       </c>
       <c r="F15" t="n">
-        <v>3.7743</v>
+        <v>3.2662</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9518</v>
+        <v>3.0311</v>
       </c>
       <c r="H15" t="n">
-        <v>0.968</v>
+        <v>1.8033</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9838</v>
+        <v>1.2278</v>
       </c>
       <c r="J15" t="n">
-        <v>1.088</v>
+        <v>1.9671</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0476</v>
+        <v>2.0875</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0405</v>
+        <v>-0.1204</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8638</v>
+        <v>1.064</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0795</v>
+        <v>-0.2842</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9433</v>
+        <v>1.3482</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9534</v>
+        <v>2.3441</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1488</v>
+        <v>2.5395</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.5619</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7024</v>
+        <v>0.3447</v>
       </c>
       <c r="U15" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.2173</v>
       </c>
       <c r="V15" t="n">
-        <v>2.4373</v>
+        <v>1.2186</v>
       </c>
       <c r="W15" t="n">
         <v>1.7731</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6642</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.9631</v>
+        <v>7.1425</v>
       </c>
       <c r="E16" t="n">
-        <v>4.0136</v>
+        <v>3.3682</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9494</v>
+        <v>3.7743</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9426</v>
+        <v>1.9518</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4047</v>
+        <v>0.968</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5379</v>
+        <v>0.9838</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7021</v>
+        <v>1.088</v>
       </c>
       <c r="K16" t="n">
-        <v>2.108</v>
+        <v>1.0476</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5942</v>
+        <v>0.0405</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2405</v>
+        <v>0.8638</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7032</v>
+        <v>-0.0795</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9437</v>
+        <v>0.9433</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7581</v>
+        <v>1.9534</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9301</v>
+        <v>2.1488</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2298</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3784</v>
+        <v>0.7024</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6082</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>2.4921</v>
+        <v>2.4373</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1052</v>
+        <v>1.7731</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3869</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>R. PALOMARES MUNOZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.9065</v>
+        <v>6.3561</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8627</v>
+        <v>3.4066</v>
       </c>
       <c r="F17" t="n">
-        <v>3.0438</v>
+        <v>2.9494</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4476</v>
+        <v>2.3357</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8276</v>
+        <v>1.4047</v>
       </c>
       <c r="I17" t="n">
-        <v>0.62</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3984</v>
+        <v>2.0951</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9915</v>
+        <v>2.108</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.0128</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0492</v>
+        <v>0.2405</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1639</v>
+        <v>-0.7032</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2132</v>
+        <v>0.9437</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1488</v>
+        <v>2.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9863</v>
+        <v>-0.2298</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1405</v>
+        <v>0.3784</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1542</v>
+        <v>-0.6082</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4959</v>
+        <v>2.4921</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4959</v>
+        <v>2.1052</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1806,7 +1887,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1874,553 +1955,921 @@
       </c>
       <c r="X18" t="n">
         <v>-1.4959</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. GONZÁLEZ BRUMOS</t>
+          <t>E. MARTIN GASCON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>5.2949</v>
+        <v>4.6785</v>
       </c>
       <c r="E19" t="n">
-        <v>3.0185</v>
+        <v>1.6348</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2764</v>
+        <v>3.0438</v>
       </c>
       <c r="G19" t="n">
-        <v>3.8132</v>
+        <v>1.2196</v>
       </c>
       <c r="H19" t="n">
-        <v>2.977</v>
+        <v>0.5996</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="J19" t="n">
-        <v>4.0376</v>
+        <v>0.1704</v>
       </c>
       <c r="K19" t="n">
-        <v>3.3359</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7017</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2245</v>
+        <v>1.0492</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3589</v>
+        <v>-0.1639</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1344</v>
+        <v>1.2132</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9301</v>
+        <v>2.1488</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1314</v>
+        <v>0.9863</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2979</v>
+        <v>1.1405</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4293</v>
+        <v>-0.1542</v>
       </c>
       <c r="V19" t="n">
-        <v>0.8317</v>
+        <v>1.4959</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8317</v>
+        <v>1.4959</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>P. GONZALEZ BRUMOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.384</v>
+        <v>3.1599</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5995</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>2.9834</v>
+        <v>2.2764</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6262</v>
+        <v>1.6782</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2492</v>
+        <v>2.0561</v>
       </c>
       <c r="I20" t="n">
-        <v>1.377</v>
+        <v>-0.3778</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5205</v>
+        <v>1.9027</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0872</v>
+        <v>2.415</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4333</v>
+        <v>-0.5122</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1057</v>
+        <v>-0.2245</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.838</v>
+        <v>-0.3589</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9437</v>
+        <v>0.1344</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.1022</v>
+        <v>-2.1488</v>
       </c>
       <c r="R20" t="n">
-        <v>3.5162</v>
+        <v>2.9301</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.152</v>
+        <v>-0.1314</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4864</v>
+        <v>0.2979</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6384</v>
+        <v>-0.4293</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4959</v>
+        <v>0.8317</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4959</v>
+        <v>0.8317</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. ROSA BEJARANO</t>
+          <t>G. LOZANO MASSANET</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.623</v>
+        <v>2.384</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0382</v>
+        <v>-0.5995</v>
       </c>
       <c r="F21" t="n">
-        <v>2.6612</v>
+        <v>2.9834</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3375</v>
+        <v>1.6262</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4344</v>
+        <v>0.2492</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9031</v>
+        <v>1.377</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7221</v>
+        <v>1.5205</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2802</v>
+        <v>1.0872</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.442</v>
+        <v>0.4333</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3846</v>
+        <v>0.1057</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1542</v>
+        <v>-0.838</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5389</v>
+        <v>0.9437</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1721</v>
+        <v>-0.586</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1721</v>
+        <v>-4.1022</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3441</v>
+        <v>3.5162</v>
       </c>
       <c r="S21" t="n">
-        <v>1.5112</v>
+        <v>-0.152</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5787</v>
+        <v>0.4864</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0675</v>
+        <v>-0.6384</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2772</v>
+        <v>1.4959</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>1.4959</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. TOLEDO CIVICO</t>
+          <t>P. GONZÁLEZ BRUMOS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.2103</v>
+        <v>2.1349</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0183</v>
+        <v>2.1349</v>
       </c>
       <c r="F22" t="n">
-        <v>1.192</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1.4841</v>
+        <v>2.1349</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8102</v>
+        <v>0.921</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6739000000000001</v>
+        <v>1.214</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6152</v>
+        <v>2.1349</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6152</v>
+        <v>0.921</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8688</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1949</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6739000000000001</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0034</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1026</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.09909999999999999</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>O. ROSA BEJARANO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4348</v>
+        <v>1.623</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3481</v>
+        <v>-1.0382</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7829</v>
+        <v>2.6612</v>
       </c>
       <c r="G23" t="n">
-        <v>1.8089</v>
+        <v>-1.3375</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0253</v>
+        <v>-0.4344</v>
       </c>
       <c r="I23" t="n">
-        <v>1.8342</v>
+        <v>-0.9031</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7449</v>
+        <v>-1.7221</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1241</v>
+        <v>-0.2802</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6208</v>
+        <v>-1.442</v>
       </c>
       <c r="M23" t="n">
-        <v>1.064</v>
+        <v>0.3846</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1494</v>
+        <v>-0.1542</v>
       </c>
       <c r="O23" t="n">
-        <v>1.2134</v>
+        <v>0.5389</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.1255</v>
+        <v>-1.1721</v>
       </c>
       <c r="R23" t="n">
-        <v>2.7348</v>
+        <v>2.3441</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5125</v>
+        <v>1.5112</v>
       </c>
       <c r="T23" t="n">
-        <v>1.0325</v>
+        <v>1.5787</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5201</v>
+        <v>-0.0675</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.4959</v>
+        <v>0.2772</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4135</v>
+        <v>1.2279</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3057</v>
+        <v>1.2279</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7192</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7317</v>
+        <v>1.2279</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2978</v>
+        <v>1.2279</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5661</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3677</v>
+        <v>1.2279</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.5296</v>
+        <v>1.2279</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1619</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3639</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7682</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4043</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1404</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2023</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. TOLEDO CIVICO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>51.4098</v>
+        <v>1.2103</v>
       </c>
       <c r="E25" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.192</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.4841</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.8102</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.6739000000000001</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.6152</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.6152</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.8688</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.1949</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.6739000000000001</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.1026</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.09909999999999999</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>R. PALOMARES MUÑOZ</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>J. LLORENTE GUILLEMI</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.4348</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-1.3481</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.7829</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.8089</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.0253</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.8342</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.7449</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.1241</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.6208</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.064</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.1494</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.2134</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-3.1255</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.7348</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.0325</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.5201</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>R. DALET CASALPRIM</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.4135</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.3057</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.7192</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.7317</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-1.2978</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.5661</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-0.3677</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-0.5296</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-0.3639</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-0.7682</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-0.1404</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-0.2023</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>play_by_play_2484199_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>51.4096</v>
+      </c>
+      <c r="E29" t="n">
         <v>20.0183</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F29" t="n">
         <v>31.3912</v>
       </c>
-      <c r="G25" t="n">
-        <v>27.43840000000001</v>
-      </c>
-      <c r="H25" t="n">
+      <c r="G29" t="n">
+        <v>27.43830000000001</v>
+      </c>
+      <c r="H29" t="n">
         <v>15.9749</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I29" t="n">
         <v>11.4636</v>
       </c>
-      <c r="J25" t="n">
-        <v>20.6172</v>
-      </c>
-      <c r="K25" t="n">
-        <v>19.9372</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.6800000000000002</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="J29" t="n">
+        <v>20.61710000000001</v>
+      </c>
+      <c r="K29" t="n">
+        <v>19.9373</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.6801000000000001</v>
+      </c>
+      <c r="M29" t="n">
         <v>6.8211</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N29" t="n">
         <v>-3.9622</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O29" t="n">
         <v>10.7836</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P29" t="n">
         <v>11.7206</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q29" t="n">
         <v>-18.5577</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R29" t="n">
         <v>30.2781</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S29" t="n">
         <v>5.048300000000001</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T29" t="n">
         <v>7.4297</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U29" t="n">
         <v>-2.3811</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V29" t="n">
         <v>7.202100000000002</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W29" t="n">
         <v>10.5289</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X29" t="n">
         <v>-3.3269</v>
       </c>
+      <c r="Y29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
